--- a/SMEAC_Master_Data.xlsx
+++ b/SMEAC_Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vargas/Documents/JW/Proyectos 2025-2026/IT-Projects-J-W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21914E81-E44E-F542-8765-6169147445C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A06746-4E36-B84F-BF31-039A91D619A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="680" windowWidth="21760" windowHeight="14080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="680" windowWidth="21760" windowHeight="14080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v1.2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="452">
   <si>
     <t>Phase</t>
   </si>
@@ -814,9 +814,6 @@
     <t>Created "42. Payroll Penalty" Karbon template and Square billing item "Assessment Protest".</t>
   </si>
   <si>
-    <t>Training Erika (Payroll Lead) on MEGA Revenue Tracker for Metas monitoring.</t>
-  </si>
-  <si>
     <t>Restarted EFTPS Batch Provider and trained Diana M. for autonomous client enrollment.</t>
   </si>
   <si>
@@ -826,9 +823,6 @@
     <t>Installation of the official JW WhatsApp Business line.</t>
   </si>
   <si>
-    <t>WhatsApp Business &amp; AI Deployment: Whatauto + Gemini linked to IG, FB, and Landing Pages.</t>
-  </si>
-  <si>
     <t>WhatsApp IA engagement tests for after-hours client lead capture.</t>
   </si>
   <si>
@@ -838,12 +832,6 @@
     <t>Finalized corrections for ten 1099 forms for Silver Tray in IRIS.</t>
   </si>
   <si>
-    <t>LedgerBot (AI Assistant) - Deployment for dynamic uploads and backup management.</t>
-  </si>
-  <si>
-    <t>Marketing Bots Evolution: Automated campaigns and advanced AI integration.</t>
-  </si>
-  <si>
     <t>Configure and add all Karbon works for the Bookkeeping department with the suggested strategies: one work per year with periodic tasks according to the service.</t>
   </si>
   <si>
@@ -1195,17 +1183,436 @@
     <t>Closing the Annual Cycle: Final identity validation and filing for high-volume accounts after IRS audit.</t>
   </si>
   <si>
-    <t>Full Deployment: Transitioning the proprietary AI assistant to real-world production environment for efficiency.</t>
-  </si>
-  <si>
-    <t>Strategic Roadmap: Scaling automated marketing through deep AI system integration and predictive analysis.</t>
+    <t>SMEAC Dashboard Architecture &amp; Governance</t>
+  </si>
+  <si>
+    <t>Feb 19-20</t>
+  </si>
+  <si>
+    <t>Comprehensive updates and synchronization of the SMEAC (Situation, Mission, Execution, Administration, Command) dashboard. Conducted a technical audit of current activities, project timelines, and CTO-level advancements to ensure the master data reflects real-time operational status.</t>
+  </si>
+  <si>
+    <t>Operational Transparency</t>
+  </si>
+  <si>
+    <t>Strategic Data Governance: Ensuring the integrity of the firm’s primary decision-making tool. This provides high-level transparency and system resilience by mapping technical milestones to business objectives, allowing for precise tracking of J&amp;W Accounting’s evolution.</t>
+  </si>
+  <si>
+    <t>Sep 08</t>
+  </si>
+  <si>
+    <t>Oct 16</t>
+  </si>
+  <si>
+    <t>Oct 20</t>
+  </si>
+  <si>
+    <t>Oct 22</t>
+  </si>
+  <si>
+    <t>Oct 24</t>
+  </si>
+  <si>
+    <t>Oct 27</t>
+  </si>
+  <si>
+    <t>Feb 05</t>
+  </si>
+  <si>
+    <t>Feb 02</t>
+  </si>
+  <si>
+    <t>Feb 03</t>
+  </si>
+  <si>
+    <t>Feb 01</t>
+  </si>
+  <si>
+    <t>Feb 04</t>
+  </si>
+  <si>
+    <t>Feb 11</t>
+  </si>
+  <si>
+    <t>Feb 13</t>
+  </si>
+  <si>
+    <t>Feb 14</t>
+  </si>
+  <si>
+    <t>Feb 16</t>
+  </si>
+  <si>
+    <t>Feb 18</t>
+  </si>
+  <si>
+    <t>LedgerBot- Deployment for dynamic uploads and backup management.</t>
+  </si>
+  <si>
+    <t>Full Deployment: Transitioning the LedgerBot to app with Sessions and Default rules.</t>
+  </si>
+  <si>
+    <t>WhatsApp Business &amp; AI Deployment: Whatauto + Gemini linked to WP, and Landing Pages.</t>
+  </si>
+  <si>
+    <t>Training Erika (Payroll Lead) on MEGA Revenue Tracker for Goals monitoring.</t>
+  </si>
+  <si>
+    <t>International Operations &amp; Logistics</t>
+  </si>
+  <si>
+    <t>Feb 24 - 26</t>
+  </si>
+  <si>
+    <t>International return transit from the United States to Colombia. Managed remote oversight of firm operations and maintained communication protocols during multi-day travel window to ensure zero downtime.</t>
+  </si>
+  <si>
+    <t>Infrastructure &amp; Continuity</t>
+  </si>
+  <si>
+    <r>
+      <t>System Resilience:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ensuring leadership availability and operational continuity during cross-border transitions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tax Season Support &amp; Compliance</t>
+  </si>
+  <si>
+    <t>Technical assistance to the Payroll Department for the correction of three (3) 1099-NEC forms for 'Silver Tray' via the IRIS (Information Returns Intake System) platform, following the late receipt of verified and accurate data from the business owner.</t>
+  </si>
+  <si>
+    <r>
+      <t>Data Governance &amp; Risk Mitigation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Executed a critical correction workflow to ensure federal compliance. Overcame delays in client data integrity by leveraging the IRIS portal to prevent late-filing penalties and ensure accurate reporting of non-employee compensation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Feb 26</t>
+  </si>
+  <si>
+    <t>Credentialing &amp; Federal Compliance</t>
+  </si>
+  <si>
+    <t>Mar 2 - 6</t>
+  </si>
+  <si>
+    <t>Full execution of the IRS Preparer Tax Identification Number (PTIN) application process. Managed document notarization and navigated a 'Foreign Status' pivot after initial denial to secure official federal acceptance.</t>
+  </si>
+  <si>
+    <r>
+      <t>Strategic Resilience &amp; R&amp;D Scalability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Overcame federal bureaucratic barriers to establish the legal framework for official representation. This provides the critical credentialing required to integrate and deploy proprietary in-house tax-prep software solutions, transforming compliance into a scalable technological asset.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sr. Consulting / Software R&amp;D</t>
+  </si>
+  <si>
+    <t>March 07</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Successfully completed the official </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IRS Paid Preparer Due Diligence Training</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Program Number: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CEQXT-T-01613-24-S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). Earned 2 IRS-validated credits, formalizing technical expertise in federal tax preparation standards.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Risk Mitigation &amp; Algorithmic Integrity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ensures all future tax-prep software developed in-house adheres to strict federal Due Diligence requirements. Minimizes firm-wide liability by certifying that human oversight and automated workflows meet IRS ethical and legal standards.</t>
+    </r>
+  </si>
+  <si>
+    <t>Legal Compliance / Quality Assurance</t>
+  </si>
+  <si>
+    <t>AI R&amp;D &amp; Advanced Compliance</t>
+  </si>
+  <si>
+    <t>March 9</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Completed CPE Course: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IRS NOTICES EXPLAINED: HOW TO ASSIST YOUR CLIENTS AND RESPOND EFFECTIVELY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Program: HURS9-T-01894-25-O). Earned 1 IRS CE Credit. Mastery of official response protocols for federal tax notices.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI Agent Training &amp; Architecture:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Technical mapping of IRS response workflows to be ingested by proprietary AI agents. This enables the automated generation of high-precision rebuttal documents and defense strategies for representation services, ensuring 100% alignment with IRS procedural requirements.</t>
+    </r>
+  </si>
+  <si>
+    <t>Software R&amp;D / Automation</t>
+  </si>
+  <si>
+    <t>Strategic Roadmap: Scaling automated marketing through deep AI system integration.</t>
+  </si>
+  <si>
+    <t>Automation &amp; Workflow Engineering</t>
+  </si>
+  <si>
+    <t>Design and implementation of an automated notification system for the Payroll Department. The solution utilizes Google Sheets as a database and Apps Script as an orchestration engine to trigger customized Gmail reminder campaigns regarding service fee collections.</t>
+  </si>
+  <si>
+    <r>
+      <t>Operational Efficiency &amp; Friction Mitigation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Automating pre-collection alerts to reduce inbound support tickets and client disputes. This technical workaround optimizes resource allocation by preventing human intervention in repetitive communication tasks and enhancing payment predictability.</t>
+    </r>
+  </si>
+  <si>
+    <t>RPA Workaround / Automation</t>
+  </si>
+  <si>
+    <t>Marketing Bots Evolution: Advanced AI integration.</t>
+  </si>
+  <si>
+    <t>Projected</t>
+  </si>
+  <si>
+    <t>Proprietary BI Architecture &amp; MEGA Dashboard Evolution</t>
+  </si>
+  <si>
+    <t>Mar 9 - Present</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Engineering the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MEGA Dashboard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the firm’s primary Business Intelligence (BI) module. Developing a dynamic </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Admin-to-User Switching Toggle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and custom data-abstraction layers to bypass Square’s native reporting limitations (lack of YoY comparisons and granular user-level segmentation).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Interoperability &amp; Advanced RBAC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Solving a critical data security gap by filtering sensitive firm-wide revenue data. The system enables General Management (Nathaly) to pivot between global metrics and individual performance views, providing high-fidelity oversight while ensuring staff only access authorized, acoted data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Software R&amp;D / Data Governance</t>
+  </si>
+  <si>
+    <t>IT Infrastructure &amp; Disaster Recovery</t>
+  </si>
+  <si>
+    <t>March 10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Comprehensive manual backup of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ProSeries 25Data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> files. Execution of data redundancy protocols by migrating tax year datasets to independent, secure external storage sources.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Business Continuity &amp; Risk Mitigation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Implementing a fail-safe data architecture to prevent information loss during Tax Season. This redundancy layer protects critical client tax records against system failures or software corruption, ensuring 100% data integrity and operational resilience.</t>
+    </r>
+  </si>
+  <si>
+    <t>Infrastructure / Risk Management</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1223,6 +1630,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1248,11 +1662,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1471,10 +1888,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1523,14 +1941,14 @@
         <v>68</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>71</v>
@@ -1559,14 +1977,14 @@
         <v>72</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -1595,14 +2013,14 @@
         <v>74</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>77</v>
@@ -1631,14 +2049,14 @@
         <v>78</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="3">
-        <v>39692</v>
+      <c r="D5" s="5" t="s">
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>77</v>
@@ -1667,14 +2085,14 @@
         <v>80</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>81</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>83</v>
@@ -1703,14 +2121,14 @@
         <v>84</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>81</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>86</v>
@@ -1739,14 +2157,14 @@
         <v>87</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>88</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>90</v>
@@ -1775,14 +2193,14 @@
         <v>91</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>94</v>
@@ -1811,14 +2229,14 @@
         <v>95</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="5" t="s">
         <v>92</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>94</v>
@@ -1847,14 +2265,14 @@
         <v>97</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="3">
-        <v>42644</v>
+      <c r="D11" s="5" t="s">
+        <v>393</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>99</v>
@@ -1883,14 +2301,14 @@
         <v>100</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>101</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>102</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>99</v>
@@ -1919,14 +2337,14 @@
         <v>103</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="3">
-        <v>44105</v>
+      <c r="D13" s="5" t="s">
+        <v>394</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>105</v>
@@ -1955,14 +2373,14 @@
         <v>106</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="3">
-        <v>44835</v>
+      <c r="D14" s="5" t="s">
+        <v>395</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>107</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>86</v>
@@ -1991,14 +2409,14 @@
         <v>108</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>109</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>111</v>
@@ -2027,14 +2445,14 @@
         <v>65</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>109</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>113</v>
@@ -2063,14 +2481,14 @@
         <v>114</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="3">
-        <v>45566</v>
+      <c r="D17" s="5" t="s">
+        <v>396</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>115</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>116</v>
@@ -2099,14 +2517,14 @@
         <v>117</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="3">
-        <v>45566</v>
+      <c r="D18" s="5" t="s">
+        <v>396</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>113</v>
@@ -2135,14 +2553,14 @@
         <v>119</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="3">
-        <v>45566</v>
+      <c r="D19" s="5" t="s">
+        <v>396</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>121</v>
@@ -2171,14 +2589,14 @@
         <v>122</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5" t="s">
         <v>101</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>123</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>124</v>
@@ -2207,14 +2625,14 @@
         <v>66</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="5" t="s">
         <v>109</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>86</v>
@@ -2243,14 +2661,14 @@
         <v>126</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="3">
-        <v>46661</v>
+      <c r="D22" s="5" t="s">
+        <v>397</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>113</v>
@@ -2279,14 +2697,14 @@
         <v>8</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="5" t="s">
         <v>127</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>157</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>128</v>
@@ -2315,14 +2733,14 @@
         <v>8</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5" t="s">
         <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>130</v>
@@ -2351,14 +2769,14 @@
         <v>8</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="5" t="s">
         <v>131</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>17</v>
@@ -2387,14 +2805,14 @@
         <v>8</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="5" t="s">
         <v>158</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>121</v>
@@ -2423,14 +2841,14 @@
         <v>10</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>99</v>
@@ -2459,14 +2877,14 @@
         <v>10</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="5" t="s">
         <v>161</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>162</v>
@@ -2495,14 +2913,14 @@
         <v>10</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>163</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>164</v>
@@ -2531,14 +2949,14 @@
         <v>165</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="5" t="s">
         <v>166</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>167</v>
@@ -2567,14 +2985,14 @@
         <v>165</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="5" t="s">
         <v>168</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>169</v>
@@ -2603,14 +3021,14 @@
         <v>165</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="5" t="s">
         <v>170</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>171</v>
@@ -2639,14 +3057,14 @@
         <v>28</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="5" t="s">
         <v>132</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>133</v>
@@ -2675,14 +3093,14 @@
         <v>28</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="5" t="s">
         <v>134</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>135</v>
@@ -2711,14 +3129,14 @@
         <v>28</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="5" t="s">
         <v>136</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>137</v>
@@ -2747,14 +3165,14 @@
         <v>29</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="5" t="s">
         <v>172</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>173</v>
@@ -2783,14 +3201,14 @@
         <v>30</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="5" t="s">
         <v>138</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>139</v>
@@ -2819,14 +3237,14 @@
         <v>27</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="5" t="s">
         <v>223</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>228</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>224</v>
@@ -2855,14 +3273,14 @@
         <v>27</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="5" t="s">
         <v>225</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>174</v>
@@ -2891,14 +3309,14 @@
         <v>31</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="5" t="s">
         <v>140</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>229</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>141</v>
@@ -2927,14 +3345,14 @@
         <v>31</v>
       </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="5" t="s">
         <v>175</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>230</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>42</v>
@@ -2963,14 +3381,14 @@
         <v>31</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>231</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>143</v>
@@ -2999,14 +3417,14 @@
         <v>31</v>
       </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="5" t="s">
         <v>176</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>232</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>177</v>
@@ -3035,14 +3453,14 @@
         <v>31</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="5" t="s">
         <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>178</v>
@@ -3071,14 +3489,14 @@
         <v>31</v>
       </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="5" t="s">
         <v>144</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>233</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>17</v>
@@ -3107,14 +3525,14 @@
         <v>31</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="5" t="s">
         <v>179</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>234</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>180</v>
@@ -3143,14 +3561,14 @@
         <v>31</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="3">
-        <v>38384</v>
+      <c r="D47" s="5" t="s">
+        <v>398</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>181</v>
@@ -3179,14 +3597,14 @@
         <v>32</v>
       </c>
       <c r="C48" s="2"/>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="5" t="s">
         <v>182</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>235</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>183</v>
@@ -3215,14 +3633,14 @@
         <v>33</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="5" t="s">
         <v>184</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>236</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>185</v>
@@ -3251,14 +3669,14 @@
         <v>33</v>
       </c>
       <c r="C50" s="2"/>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="5" t="s">
         <v>186</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>237</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>86</v>
@@ -3287,14 +3705,14 @@
         <v>33</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="5" t="s">
         <v>186</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>86</v>
@@ -3323,14 +3741,14 @@
         <v>33</v>
       </c>
       <c r="C52" s="2"/>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="5" t="s">
         <v>187</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>239</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>86</v>
@@ -3359,14 +3777,14 @@
         <v>33</v>
       </c>
       <c r="C53" s="2"/>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="5" t="s">
         <v>188</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>189</v>
@@ -3395,14 +3813,14 @@
         <v>34</v>
       </c>
       <c r="C54" s="2"/>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="5" t="s">
         <v>190</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>83</v>
@@ -3431,14 +3849,14 @@
         <v>35</v>
       </c>
       <c r="C55" s="2"/>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="5" t="s">
         <v>182</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>240</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>46</v>
@@ -3467,14 +3885,14 @@
         <v>35</v>
       </c>
       <c r="C56" s="2"/>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="5" t="s">
         <v>182</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>241</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>46</v>
@@ -3503,14 +3921,14 @@
         <v>35</v>
       </c>
       <c r="C57" s="2"/>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="5" t="s">
         <v>226</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>227</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>46</v>
@@ -3539,14 +3957,14 @@
         <v>35</v>
       </c>
       <c r="C58" s="2"/>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="5" t="s">
         <v>191</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>242</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>192</v>
@@ -3575,14 +3993,14 @@
         <v>36</v>
       </c>
       <c r="C59" s="2"/>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="5" t="s">
         <v>175</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>193</v>
@@ -3611,14 +4029,14 @@
         <v>37</v>
       </c>
       <c r="C60" s="2"/>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="5" t="s">
         <v>145</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>243</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>194</v>
@@ -3647,14 +4065,14 @@
         <v>38</v>
       </c>
       <c r="C61" s="2"/>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="5" t="s">
         <v>146</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>244</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>60</v>
@@ -3683,14 +4101,14 @@
         <v>39</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>245</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>196</v>
@@ -3719,14 +4137,14 @@
         <v>38</v>
       </c>
       <c r="C63" s="2"/>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="5" t="s">
         <v>197</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>246</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>198</v>
@@ -3755,14 +4173,14 @@
         <v>40</v>
       </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="5" t="s">
         <v>147</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>148</v>
@@ -3791,14 +4209,14 @@
         <v>41</v>
       </c>
       <c r="C65" s="2"/>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="5" t="s">
         <v>199</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>247</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>200</v>
@@ -3827,14 +4245,14 @@
         <v>42</v>
       </c>
       <c r="C66" s="2"/>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>248</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>201</v>
@@ -3863,14 +4281,14 @@
         <v>43</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>249</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>202</v>
@@ -3899,14 +4317,14 @@
         <v>44</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="3">
-        <v>37288</v>
+      <c r="D68" s="5" t="s">
+        <v>399</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>203</v>
@@ -3929,20 +4347,20 @@
     </row>
     <row r="69" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="5" t="s">
         <v>204</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>250</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>205</v>
@@ -3965,20 +4383,20 @@
     </row>
     <row r="70" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C70" s="2"/>
-      <c r="D70" s="3">
-        <v>37288</v>
+      <c r="D70" s="5" t="s">
+        <v>399</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>251</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>60</v>
@@ -4001,20 +4419,20 @@
     </row>
     <row r="71" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C71" s="2"/>
-      <c r="D71" s="3">
-        <v>37653</v>
+      <c r="D71" s="5" t="s">
+        <v>400</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>206</v>
@@ -4037,20 +4455,20 @@
     </row>
     <row r="72" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="2"/>
-      <c r="D72" s="3">
-        <v>36923</v>
+      <c r="D72" s="5" t="s">
+        <v>401</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>252</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>23</v>
@@ -4073,20 +4491,20 @@
     </row>
     <row r="73" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C73" s="2"/>
-      <c r="D73" s="3">
-        <v>38018</v>
+      <c r="D73" s="5" t="s">
+        <v>402</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>253</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>207</v>
@@ -4109,20 +4527,20 @@
     </row>
     <row r="74" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="3">
-        <v>38018</v>
+      <c r="D74" s="5" t="s">
+        <v>402</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>254</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>208</v>
@@ -4145,20 +4563,20 @@
     </row>
     <row r="75" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C75" s="2"/>
-      <c r="D75" s="3">
-        <v>38018</v>
+      <c r="D75" s="5" t="s">
+        <v>402</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>255</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>209</v>
@@ -4181,20 +4599,20 @@
     </row>
     <row r="76" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C76" s="2"/>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="5" t="s">
         <v>210</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>256</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4217,20 +4635,20 @@
     </row>
     <row r="77" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="5" t="s">
         <v>179</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>257</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>211</v>
@@ -4251,20 +4669,20 @@
     </row>
     <row r="78" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C78" s="2"/>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>150</v>
@@ -4278,20 +4696,20 @@
     </row>
     <row r="79" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C79" s="2"/>
-      <c r="D79" s="3">
-        <v>38384</v>
+      <c r="D79" s="5" t="s">
+        <v>398</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>258</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>212</v>
@@ -4305,20 +4723,20 @@
     </row>
     <row r="80" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C80" s="2"/>
-      <c r="D80" s="3">
-        <v>38384</v>
+      <c r="D80" s="5" t="s">
+        <v>398</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>213</v>
@@ -4332,20 +4750,20 @@
     </row>
     <row r="81" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C81" s="2"/>
-      <c r="D81" s="3">
-        <v>38018</v>
+      <c r="D81" s="5" t="s">
+        <v>402</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>259</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>214</v>
@@ -4359,20 +4777,20 @@
     </row>
     <row r="82" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C82" s="2"/>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="5" t="s">
         <v>215</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>260</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>216</v>
@@ -4386,20 +4804,20 @@
     </row>
     <row r="83" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C83" s="2"/>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="5" t="s">
         <v>151</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>261</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>152</v>
@@ -4413,20 +4831,20 @@
     </row>
     <row r="84" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C84" s="2"/>
-      <c r="D84" s="3">
-        <v>40575</v>
+      <c r="D84" s="5" t="s">
+        <v>403</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>262</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>217</v>
@@ -4440,20 +4858,20 @@
     </row>
     <row r="85" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C85" s="2"/>
-      <c r="D85" s="3">
-        <v>41306</v>
+      <c r="D85" s="5" t="s">
+        <v>404</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>263</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>153</v>
@@ -4467,20 +4885,20 @@
     </row>
     <row r="86" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C86" s="2"/>
-      <c r="D86" s="3">
-        <v>41306</v>
+      <c r="D86" s="5" t="s">
+        <v>404</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>264</v>
+        <v>411</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>218</v>
@@ -4494,20 +4912,20 @@
     </row>
     <row r="87" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C87" s="2"/>
-      <c r="D87" s="3">
-        <v>41306</v>
+      <c r="D87" s="5" t="s">
+        <v>404</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>219</v>
@@ -4521,20 +4939,20 @@
     </row>
     <row r="88" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C88" s="2"/>
-      <c r="D88" s="3">
-        <v>41306</v>
+      <c r="D88" s="5" t="s">
+        <v>404</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>154</v>
@@ -4554,14 +4972,14 @@
         <v>58</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="3">
-        <v>41671</v>
+      <c r="D89" s="5" t="s">
+        <v>405</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>220</v>
@@ -4581,14 +4999,14 @@
         <v>20</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="5" t="s">
         <v>221</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>268</v>
+        <v>410</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>21</v>
@@ -4608,14 +5026,14 @@
         <v>59</v>
       </c>
       <c r="C91" s="2"/>
-      <c r="D91" s="3">
-        <v>42401</v>
+      <c r="D91" s="5" t="s">
+        <v>406</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>155</v>
@@ -4629,20 +5047,20 @@
     </row>
     <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C92" s="2"/>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="5" t="s">
         <v>156</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>18</v>
@@ -4656,20 +5074,20 @@
     </row>
     <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C93" s="2"/>
-      <c r="D93" s="3">
-        <v>43132</v>
+      <c r="D93" s="5" t="s">
+        <v>407</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>222</v>
@@ -4682,60 +5100,300 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="3">
-        <v>36923</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F94" s="2" t="s">
+      <c r="A94" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C94" s="4"/>
+      <c r="D94" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F94" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" s="2" t="s">
+      <c r="G94" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I94" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>26</v>
+      <c r="A95" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="G95" s="2" t="s">
+      <c r="E102" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H95" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I95" s="2" t="s">
+      <c r="H102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I104" s="2" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/SMEAC_Master_Data.xlsx
+++ b/SMEAC_Master_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vargas/Documents/JW/Proyectos 2025-2026/IT-Projects-J-W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A06746-4E36-B84F-BF31-039A91D619A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE22E9D-2C23-7143-B112-9BBBB428638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="680" windowWidth="21760" windowHeight="14080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="68" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>44</v>

--- a/SMEAC_Master_Data.xlsx
+++ b/SMEAC_Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vargas/Documents/JW/Proyectos 2025-2026/IT-Projects-J-W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE22E9D-2C23-7143-B112-9BBBB428638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB72CB6-18B3-AE48-BA3B-C9898F57AB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="680" windowWidth="21760" windowHeight="14080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="680" windowWidth="25460" windowHeight="18780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v1.2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="447">
   <si>
     <t>Phase</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Strategic Audit &amp; Configuration (Square)</t>
   </si>
   <si>
-    <t>Progress</t>
-  </si>
-  <si>
     <t>Phase 2</t>
   </si>
   <si>
@@ -76,33 +73,18 @@
     <t>Data Integrity</t>
   </si>
   <si>
-    <t>Data Recovery</t>
-  </si>
-  <si>
     <t>UX Optimization</t>
   </si>
   <si>
-    <t>Omnichannel Marketing &amp; AI Integration</t>
-  </si>
-  <si>
-    <t>Lead Automation</t>
-  </si>
-  <si>
     <t>Team Enablement (AI Training)</t>
   </si>
   <si>
     <t>User Enablement</t>
   </si>
   <si>
-    <t>Evolution &amp; Growth (Advances)</t>
-  </si>
-  <si>
     <t>Checkout Efficiency</t>
   </si>
   <si>
-    <t>Evolution &amp; Growth (Pending)</t>
-  </si>
-  <si>
     <t>Logistics</t>
   </si>
   <si>
@@ -151,12 +133,6 @@
     <t>Branding</t>
   </si>
   <si>
-    <t>Systems Visibility (SSoT)</t>
-  </si>
-  <si>
-    <t>Strategic Consulting</t>
-  </si>
-  <si>
     <t>Automation Debugging</t>
   </si>
   <si>
@@ -196,12 +172,6 @@
     <t>Cloud &amp; Cost Management</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
-    <t>AI R&amp;D</t>
-  </si>
-  <si>
     <t>Compliance</t>
   </si>
   <si>
@@ -487,9 +457,6 @@
     <t>Cost Efficiency</t>
   </si>
   <si>
-    <t>Sales Automation</t>
-  </si>
-  <si>
     <t>Feb 17 - 18</t>
   </si>
   <si>
@@ -628,12 +595,6 @@
     <t>Visual Identity</t>
   </si>
   <si>
-    <t>BI</t>
-  </si>
-  <si>
-    <t>Sr Consulting</t>
-  </si>
-  <si>
     <t>Feb 2 - 3</t>
   </si>
   <si>
@@ -682,12 +643,6 @@
     <t>Autonomy</t>
   </si>
   <si>
-    <t>Omnichannel</t>
-  </si>
-  <si>
-    <t>Feb 14 - 18</t>
-  </si>
-  <si>
     <t>Season Closure</t>
   </si>
   <si>
@@ -769,9 +724,6 @@
     <t>Attended professional photography session for the firm's web portal.</t>
   </si>
   <si>
-    <t>Unified Data Connector &amp; Advanced Dashboards for 360 operation visibility.</t>
-  </si>
-  <si>
     <t>Bot adjustment for Christian's personal tax appointments (Auto-accept logic fix).</t>
   </si>
   <si>
@@ -820,15 +772,6 @@
     <t>Re-architected Replit for PayrollTools using non-autoscaling dedicated VMs.</t>
   </si>
   <si>
-    <t>Installation of the official JW WhatsApp Business line.</t>
-  </si>
-  <si>
-    <t>WhatsApp IA engagement tests for after-hours client lead capture.</t>
-  </si>
-  <si>
-    <t>Technical recreation of COTO SOLORZANO profile in Karbon after accidental deletion.</t>
-  </si>
-  <si>
     <t>Finalized corrections for ten 1099 forms for Silver Tray in IRIS.</t>
   </si>
   <si>
@@ -880,9 +823,6 @@
     <t>Implementing data redundancy and disaster recovery protocols for historical tax records.</t>
   </si>
   <si>
-    <t>Developed the Final Version of the Deleon Creative LLC Contract with an AI-blinded response strategy.</t>
-  </si>
-  <si>
     <t>Regulatory Catch-up: Finalizing extensions to avoid late-filing penalties for clients.</t>
   </si>
   <si>
@@ -895,9 +835,6 @@
     <t>RPA Cloud scaling and billing/feasibility evaluation after the Square platform update.</t>
   </si>
   <si>
-    <t>24/7 client engagement automation via proprietary conversational AI agents.</t>
-  </si>
-  <si>
     <t>Legacy Data Quality Diagnosis: Identifying 82% "noise" in the original database to prevent systemic inefficiency and data corruption.</t>
   </si>
   <si>
@@ -1060,9 +997,6 @@
     <t>Expert Data Engineering: Formatting complex CSV structures for massive contractor reporting requirements.</t>
   </si>
   <si>
-    <t>Strategic Roadmap: Deep API integration for 360° operational visibility and advanced BI control.</t>
-  </si>
-  <si>
     <t>Maintaining RPA reliability through iterative debugging of specific user permissions and edge cases.</t>
   </si>
   <si>
@@ -1126,15 +1060,6 @@
     <t>Coordinating professional brand updates and professional image alignment for digital platforms.</t>
   </si>
   <si>
-    <t>Senior Strategy &amp; Consulting: Counteracted external AI suggestions with a shielded contractual response to protect firm interests.</t>
-  </si>
-  <si>
-    <t>Final Deleon contract review: Florida Law consistency, salary evolution, and employment status audit.</t>
-  </si>
-  <si>
-    <t>High-Level Senior Consulting: Ensuring labor law compliance and resolving employment status conflicts (Ana as Employee/Employer).</t>
-  </si>
-  <si>
     <t>User Enablement: Training staff on proprietary AI assistant tools to optimize internal financial processing.</t>
   </si>
   <si>
@@ -1171,15 +1096,6 @@
     <t>Infrastructure Cost Engineering: Redesigning deployments to eliminate billing spikes and improve resource efficiency.</t>
   </si>
   <si>
-    <t>Establishing official corporate communication channels for high-level client support and security.</t>
-  </si>
-  <si>
-    <t>Building an automated lead engagement ecosystem using social media CTAs and conversational AI agents.</t>
-  </si>
-  <si>
-    <t>Disaster Recovery: Restoring CRM database integrity and service continuity after critical human error.</t>
-  </si>
-  <si>
     <t>Closing the Annual Cycle: Final identity validation and filing for high-volume accounts after IRS audit.</t>
   </si>
   <si>
@@ -1222,9 +1138,6 @@
     <t>Feb 02</t>
   </si>
   <si>
-    <t>Feb 03</t>
-  </si>
-  <si>
     <t>Feb 01</t>
   </si>
   <si>
@@ -1237,12 +1150,6 @@
     <t>Feb 13</t>
   </si>
   <si>
-    <t>Feb 14</t>
-  </si>
-  <si>
-    <t>Feb 16</t>
-  </si>
-  <si>
     <t>Feb 18</t>
   </si>
   <si>
@@ -1250,9 +1157,6 @@
   </si>
   <si>
     <t>Full Deployment: Transitioning the LedgerBot to app with Sessions and Default rules.</t>
-  </si>
-  <si>
-    <t>WhatsApp Business &amp; AI Deployment: Whatauto + Gemini linked to WP, and Landing Pages.</t>
   </si>
   <si>
     <t>Training Erika (Payroll Lead) on MEGA Revenue Tracker for Goals monitoring.</t>
@@ -1309,9 +1213,6 @@
     <t>Feb 26</t>
   </si>
   <si>
-    <t>Credentialing &amp; Federal Compliance</t>
-  </si>
-  <si>
     <t>Mar 2 - 6</t>
   </si>
   <si>
@@ -1334,9 +1235,6 @@
   </si>
   <si>
     <t>Sr. Consulting / Software R&amp;D</t>
-  </si>
-  <si>
-    <t>March 07</t>
   </si>
   <si>
     <r>
@@ -1404,12 +1302,6 @@
     <t>Legal Compliance / Quality Assurance</t>
   </si>
   <si>
-    <t>AI R&amp;D &amp; Advanced Compliance</t>
-  </si>
-  <si>
-    <t>March 9</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Completed CPE Course: </t>
     </r>
@@ -1490,9 +1382,6 @@
     <t>Proprietary BI Architecture &amp; MEGA Dashboard Evolution</t>
   </si>
   <si>
-    <t>Mar 9 - Present</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Engineering the </t>
     </r>
@@ -1561,9 +1450,6 @@
     <t>IT Infrastructure &amp; Disaster Recovery</t>
   </si>
   <si>
-    <t>March 10</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Comprehensive manual backup of </t>
     </r>
@@ -1607,12 +1493,530 @@
   <si>
     <t>Infrastructure / Risk Management</t>
   </si>
+  <si>
+    <t>Financial Systems &amp; API Infrastructure</t>
+  </si>
+  <si>
+    <t>Mar 11-12</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Responded to Co-Owner Christian Velasquez regarding Square daily sales report timing. Conducted a technical audit of Square’s settlement windows and bank clearing cycles. Identified that shifting the closing time from 8:00 PM to 11:00 PM triggers a 48-hour delay in fund availability. Evaluated Square's "Instant Transfer" 1.95% fee and rejected it. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implemented a hybrid configuration: optimized the cutoff to 12:00 AM (midnight) to capture a full 24-hour cycle (including late-night invoices) without additional settlement delays. Scheduled a rollback to the original 8:00 PM configuration for April 17 to restore 24-hour liquidity (T+1) post-peak season.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Data Governance &amp; Cash Flow Optimization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Orchestrated a strategic workaround to balance operational visibility against liquidity needs. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Engineered a hybrid scheduling model: prioritizing 24H data integrity during Tax Season and transitioning back to accelerated cash flow (Next-Day Refund) post-April 17.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mitigated unnecessary overhead while ensuring system resilience.</t>
+    </r>
+  </si>
+  <si>
+    <t>Financial Infrastructure / RPA Workaround</t>
+  </si>
+  <si>
+    <t>Mar 07</t>
+  </si>
+  <si>
+    <t>Mar 9</t>
+  </si>
+  <si>
+    <t>Mar 10</t>
+  </si>
+  <si>
+    <t>Evolution &amp; Growth</t>
+  </si>
+  <si>
+    <t>Strategic High-Level Consulting</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Engineered the Final Version of the Deleon Creative LLC Contract incorporating an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI-Shielded Response Strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Detected that external contract modifications were being autonomously generated by third-party AI; developed a counter-strategy to neutralize non-expert algorithmic suggestions. Provided CEO Diego with the final instrument and the precise technical framework for contractual drafting.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Adversarial AI Mitigation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Protecting firm interests by identifying and neutralizing hallucinated or suboptimal AI-generated legal clauses. Established a "Shielded Response" protocol to maintain human-expert governance over automated interference.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Performed final forensic audit of the DeLeon contract. Identified critical date inconsistencies and validated salary evolution parameters. Addressed a high-risk structural conflict regarding </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Florida Labor Law (Dual Employee/Employer status for Ana)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Strategically withheld a new redacted document to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prevent recursive AI friction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, delivering instead a final expert resolution. Case closed to full client satisfaction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Legal-Technical Compliance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resolved complex employment status paradoxes under Florida jurisdiction. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Advanced Consulting:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Utilized a "Communication-Only" strategy to bypass the client's AI feedback loop, ensuring structural integrity without triggering further automated errors.</t>
+    </r>
+  </si>
+  <si>
+    <t>Feb 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 3 </t>
+  </si>
+  <si>
+    <t>Omnichannel AI Integration &amp; Lead Governance</t>
+  </si>
+  <si>
+    <t>Feb 14 - Ongoing</t>
+  </si>
+  <si>
+    <r>
+      <t>Interoperability &amp; AI Governance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Establishing the foundational "Zero-Latency" lead capture system. By utilizing a proprietary System Prompt and API-level integration, we are securing a scalable, 24/7 automated response ecosystem that bypasses manual oversight while maintaining brand voice and data integrity.</t>
+    </r>
+  </si>
+  <si>
+    <t>AI Ecosystem Deployment</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Mar 9 - Ongoing</t>
+  </si>
+  <si>
+    <r>
+      <t>Official WhatsApp Business &amp; Gemini AI Infrastructure Deployment:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Successfully provisioned the official J&amp;W WhatsApp Business line. Engineered a direct API bridge using a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Google AI Studio Token</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and the WhatAuto middleware to link conversational flows with a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gemini Flash model</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Developed and deployed the initial </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>System Prompt Architecture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to define the AI's persona, constraints, and business logic for preliminary engagement testing.</t>
+    </r>
+  </si>
+  <si>
+    <t>Financial Data Governance &amp; Forensic Audit</t>
+  </si>
+  <si>
+    <t>Mar 13 - 14</t>
+  </si>
+  <si>
+    <r>
+      <t>Massive Systemic Data Recovery &amp; Audit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Initiated an emergency technical intervention following a report from Management containing critical email discrepancies. Identified that the source of the error was an external report with misaligned data that compromised profile integrity. To resolve this, I engineered a high-scale extraction of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5,932 total client records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> via Square API. Conducted a targeted forensic audit of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3,889 individual accounts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to isolate a legacy "column-shift" error. After an exhaustive profile-by-profile verification to protect recent manual updates, I executed a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bulk API restoration of 157 corrupted records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, re-establishing the "Source of Truth" for the firm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Advanced System Resilience:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mitigated the high-risk fallout of data corruption originated at the managerial report level. This operation required extensive technical man-hours to reconstruct data lineage without original CSV logs. It highlights that even minor misalignments in bulk data processing at high levels can trigger massive technical debt, necessitating senior-level intervention to ensure 100% billing accuracy and prevent legal-compliance failures.</t>
+    </r>
+  </si>
+  <si>
+    <t>Forensic Audit &amp; API Restoration</t>
+  </si>
+  <si>
+    <t>CRM Disaster Recovery &amp; Data Integrity</t>
+  </si>
+  <si>
+    <r>
+      <t>Emergency Structural Reconstruction:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Recreated the comprehensive Karbon profile for </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>COTO SOLORZANO, HUGO ERNESTO &amp; ALVARADO ORELLANA, DIANA - 4670</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> following an accidental deletion. Utilized legacy </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unique Client ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mapping and historical process logs to restore profile metadata. Re-established the technical link between the individual and the associated corporate entity. Manually reconstructed the specific Tax Work item and audited the workstream to identify missing documentation, providing a precise recovery roadmap for the staff to finalize the file.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Business Continuity &amp; Crisis Management:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mitigated the impact of human error on the firm’s core CRM. By leveraging the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unique Client ID architecture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, I ensured that the restored data remained consistent with the global database. This operation required high-tier attention to detail to ensure no historical tax data was lost, emphasizing that a single accidental deletion necessitates a multi-day technical recovery to guarantee service continuity.</t>
+    </r>
+  </si>
+  <si>
+    <t>Disaster Recovery / Integrity</t>
+  </si>
+  <si>
+    <t>Strategic Federal Credentialing &amp; AI Compliance</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1637,6 +2041,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1888,11 +2300,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S104"/>
+  <dimension ref="A1:S103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="5" max="5" width="84.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1915,13 +2327,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -1938,26 +2350,26 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1974,26 +2386,26 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -2010,26 +2422,26 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -2046,26 +2458,26 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="5" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -2082,26 +2494,26 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -2118,26 +2530,26 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -2154,26 +2566,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -2190,26 +2602,26 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -2226,26 +2638,26 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -2262,26 +2674,26 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="5" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -2298,26 +2710,26 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -2334,26 +2746,26 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="5" t="s">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -2370,26 +2782,26 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="5" t="s">
-        <v>395</v>
+        <v>367</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -2406,26 +2818,26 @@
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -2442,26 +2854,26 @@
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -2478,26 +2890,26 @@
         <v>7</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="5" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -2514,26 +2926,26 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="5" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -2550,26 +2962,26 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="5" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -2586,26 +2998,26 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -2622,26 +3034,26 @@
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -2658,26 +3070,26 @@
         <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="5" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -2698,22 +3110,22 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -2734,22 +3146,22 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -2770,22 +3182,22 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
@@ -2806,22 +3218,22 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="5" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -2842,22 +3254,22 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="5" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -2878,22 +3290,22 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="5" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -2914,22 +3326,22 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -2946,26 +3358,26 @@
         <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="5" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -2982,26 +3394,26 @@
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="5" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -3018,26 +3430,26 @@
         <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="5" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -3051,29 +3463,29 @@
     </row>
     <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="5" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -3087,29 +3499,29 @@
     </row>
     <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="5" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
@@ -3123,29 +3535,29 @@
     </row>
     <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
@@ -3159,29 +3571,29 @@
     </row>
     <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="5" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -3195,29 +3607,29 @@
     </row>
     <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="5" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -3231,29 +3643,29 @@
     </row>
     <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="5" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -3267,29 +3679,29 @@
     </row>
     <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
@@ -3303,29 +3715,29 @@
     </row>
     <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="5" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -3339,29 +3751,29 @@
     </row>
     <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="5" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3375,29 +3787,29 @@
     </row>
     <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -3411,29 +3823,29 @@
     </row>
     <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="5" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
@@ -3447,29 +3859,29 @@
     </row>
     <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
@@ -3483,29 +3895,29 @@
     </row>
     <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
@@ -3519,29 +3931,29 @@
     </row>
     <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="5" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
@@ -3555,29 +3967,29 @@
     </row>
     <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="5" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -3591,29 +4003,29 @@
     </row>
     <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="5" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
@@ -3627,29 +4039,29 @@
     </row>
     <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -3663,29 +4075,29 @@
     </row>
     <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="5" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
@@ -3699,29 +4111,29 @@
     </row>
     <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="5" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
@@ -3735,29 +4147,29 @@
     </row>
     <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="5" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
@@ -3771,29 +4183,29 @@
     </row>
     <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="5" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3807,29 +4219,29 @@
     </row>
     <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
@@ -3843,29 +4255,29 @@
     </row>
     <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="5" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
@@ -3879,29 +4291,29 @@
     </row>
     <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="5" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -3915,29 +4327,29 @@
     </row>
     <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="5" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
@@ -3951,29 +4363,29 @@
     </row>
     <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="5" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
@@ -3987,29 +4399,29 @@
     </row>
     <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="5" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
@@ -4023,29 +4435,29 @@
     </row>
     <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
@@ -4059,29 +4471,29 @@
     </row>
     <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="5" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -4095,29 +4507,29 @@
     </row>
     <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="5" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
@@ -4131,29 +4543,29 @@
     </row>
     <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
@@ -4167,29 +4579,29 @@
     </row>
     <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
@@ -4203,29 +4615,29 @@
     </row>
     <row r="65" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="5" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -4239,29 +4651,29 @@
     </row>
     <row r="66" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="5" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
@@ -4275,29 +4687,29 @@
     </row>
     <row r="67" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>43</v>
+        <v>423</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="5" t="s">
-        <v>14</v>
+        <v>428</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>346</v>
+        <v>424</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
@@ -4309,31 +4721,31 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>44</v>
+        <v>423</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="5" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>368</v>
+        <v>426</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
@@ -4347,29 +4759,29 @@
     </row>
     <row r="69" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="5" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
@@ -4383,29 +4795,29 @@
     </row>
     <row r="70" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="5" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
@@ -4419,34 +4831,34 @@
     </row>
     <row r="71" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="5" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>369</v>
+        <v>236</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
-      <c r="N71" s="3"/>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" s="2"/>
@@ -4455,34 +4867,34 @@
     </row>
     <row r="72" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="5" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>371</v>
+        <v>268</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+      <c r="N72" s="3"/>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
       <c r="Q72" s="2"/>
@@ -4491,34 +4903,34 @@
     </row>
     <row r="73" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="5" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
-      <c r="N73" s="3"/>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
@@ -4527,34 +4939,34 @@
     </row>
     <row r="74" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="5" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+      <c r="N74" s="3"/>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
       <c r="Q74" s="2"/>
@@ -4563,29 +4975,29 @@
     </row>
     <row r="75" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="5" t="s">
-        <v>402</v>
+        <v>197</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>348</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>209</v>
+        <v>17</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
@@ -4599,797 +5011,761 @@
     </row>
     <row r="76" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="5" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
-      <c r="N76" s="3"/>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
     </row>
     <row r="77" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="5" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="78" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="5" t="s">
-        <v>149</v>
+        <v>370</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="5" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="5" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>377</v>
+        <v>327</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="5" t="s">
-        <v>402</v>
+        <v>202</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="5" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="5" t="s">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="5" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="5" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="5" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>411</v>
+        <v>248</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="13" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="5" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>57</v>
+        <v>442</v>
       </c>
       <c r="C88" s="2"/>
-      <c r="D88" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>382</v>
+      <c r="D88" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>154</v>
+        <v>445</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="5" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>64</v>
+      <c r="A90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C90" s="4"/>
+      <c r="D90" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>59</v>
+      <c r="A91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="5" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>291</v>
+        <v>382</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>155</v>
+        <v>383</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
+      <c r="B93" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B94" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2" t="s">
-        <v>413</v>
+      <c r="B95" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I95" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="1" t="s">
+      <c r="I95" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>418</v>
+      <c r="B96" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>94</v>
+        <v>433</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>9</v>
+        <v>434</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>422</v>
+        <v>406</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>435</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>9</v>
+        <v>434</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="1" t="s">
+      <c r="E99" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="E100" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>445</v>
+        <v>377</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>446</v>
+        <v>20</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>64</v>
+        <v>14</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="C101" s="2"/>
-      <c r="D101" s="2" t="s">
-        <v>441</v>
+      <c r="D101" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>26</v>
+        <v>414</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="5" t="s">
-        <v>14</v>
+        <v>415</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>435</v>
+        <v>416</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>61</v>
+        <v>418</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>24</v>
+        <v>437</v>
       </c>
       <c r="C103" s="2"/>
-      <c r="D103" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>409</v>
+      <c r="D103" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>25</v>
+        <v>441</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/SMEAC_Master_Data.xlsx
+++ b/SMEAC_Master_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vargas/Documents/JW/Proyectos 2025-2026/IT-Projects-J-W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB72CB6-18B3-AE48-BA3B-C9898F57AB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C874D27A-53FB-7F45-97A2-800467C965C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="680" windowWidth="25460" windowHeight="18780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="472">
   <si>
     <t>Phase</t>
   </si>
@@ -1429,6 +1429,762 @@
     </r>
   </si>
   <si>
+    <t>Software R&amp;D / Data Governance</t>
+  </si>
+  <si>
+    <t>IT Infrastructure &amp; Disaster Recovery</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Comprehensive manual backup of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ProSeries 25Data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> files. Execution of data redundancy protocols by migrating tax year datasets to independent, secure external storage sources.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Business Continuity &amp; Risk Mitigation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Implementing a fail-safe data architecture to prevent information loss during Tax Season. This redundancy layer protects critical client tax records against system failures or software corruption, ensuring 100% data integrity and operational resilience.</t>
+    </r>
+  </si>
+  <si>
+    <t>Infrastructure / Risk Management</t>
+  </si>
+  <si>
+    <t>Financial Systems &amp; API Infrastructure</t>
+  </si>
+  <si>
+    <t>Mar 11-12</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Responded to Co-Owner Christian Velasquez regarding Square daily sales report timing. Conducted a technical audit of Square’s settlement windows and bank clearing cycles. Identified that shifting the closing time from 8:00 PM to 11:00 PM triggers a 48-hour delay in fund availability. Evaluated Square's "Instant Transfer" 1.95% fee and rejected it. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implemented a hybrid configuration: optimized the cutoff to 12:00 AM (midnight) to capture a full 24-hour cycle (including late-night invoices) without additional settlement delays. Scheduled a rollback to the original 8:00 PM configuration for April 17 to restore 24-hour liquidity (T+1) post-peak season.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Data Governance &amp; Cash Flow Optimization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Orchestrated a strategic workaround to balance operational visibility against liquidity needs. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Engineered a hybrid scheduling model: prioritizing 24H data integrity during Tax Season and transitioning back to accelerated cash flow (Next-Day Refund) post-April 17.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mitigated unnecessary overhead while ensuring system resilience.</t>
+    </r>
+  </si>
+  <si>
+    <t>Financial Infrastructure / RPA Workaround</t>
+  </si>
+  <si>
+    <t>Mar 07</t>
+  </si>
+  <si>
+    <t>Mar 9</t>
+  </si>
+  <si>
+    <t>Mar 10</t>
+  </si>
+  <si>
+    <t>Evolution &amp; Growth</t>
+  </si>
+  <si>
+    <t>Strategic High-Level Consulting</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Engineered the Final Version of the Deleon Creative LLC Contract incorporating an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI-Shielded Response Strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Detected that external contract modifications were being autonomously generated by third-party AI; developed a counter-strategy to neutralize non-expert algorithmic suggestions. Provided CEO Diego with the final instrument and the precise technical framework for contractual drafting.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Adversarial AI Mitigation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Protecting firm interests by identifying and neutralizing hallucinated or suboptimal AI-generated legal clauses. Established a "Shielded Response" protocol to maintain human-expert governance over automated interference.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Performed final forensic audit of the DeLeon contract. Identified critical date inconsistencies and validated salary evolution parameters. Addressed a high-risk structural conflict regarding </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Florida Labor Law (Dual Employee/Employer status for Ana)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Strategically withheld a new redacted document to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prevent recursive AI friction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, delivering instead a final expert resolution. Case closed to full client satisfaction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Legal-Technical Compliance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resolved complex employment status paradoxes under Florida jurisdiction. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Advanced Consulting:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Utilized a "Communication-Only" strategy to bypass the client's AI feedback loop, ensuring structural integrity without triggering further automated errors.</t>
+    </r>
+  </si>
+  <si>
+    <t>Feb 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 3 </t>
+  </si>
+  <si>
+    <t>Omnichannel AI Integration &amp; Lead Governance</t>
+  </si>
+  <si>
+    <t>Feb 14 - Ongoing</t>
+  </si>
+  <si>
+    <r>
+      <t>Interoperability &amp; AI Governance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Establishing the foundational "Zero-Latency" lead capture system. By utilizing a proprietary System Prompt and API-level integration, we are securing a scalable, 24/7 automated response ecosystem that bypasses manual oversight while maintaining brand voice and data integrity.</t>
+    </r>
+  </si>
+  <si>
+    <t>AI Ecosystem Deployment</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <r>
+      <t>Official WhatsApp Business &amp; Gemini AI Infrastructure Deployment:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Successfully provisioned the official J&amp;W WhatsApp Business line. Engineered a direct API bridge using a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Google AI Studio Token</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and the WhatAuto middleware to link conversational flows with a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gemini Flash model</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Developed and deployed the initial </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>System Prompt Architecture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to define the AI's persona, constraints, and business logic for preliminary engagement testing.</t>
+    </r>
+  </si>
+  <si>
+    <t>Financial Data Governance &amp; Forensic Audit</t>
+  </si>
+  <si>
+    <t>Mar 13 - 14</t>
+  </si>
+  <si>
+    <r>
+      <t>Massive Systemic Data Recovery &amp; Audit:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Initiated an emergency technical intervention following a report from Management containing critical email discrepancies. Identified that the source of the error was an external report with misaligned data that compromised profile integrity. To resolve this, I engineered a high-scale extraction of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5,932 total client records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> via Square API. Conducted a targeted forensic audit of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3,889 individual accounts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to isolate a legacy "column-shift" error. After an exhaustive profile-by-profile verification to protect recent manual updates, I executed a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bulk API restoration of 157 corrupted records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, re-establishing the "Source of Truth" for the firm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Advanced System Resilience:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mitigated the high-risk fallout of data corruption originated at the managerial report level. This operation required extensive technical man-hours to reconstruct data lineage without original CSV logs. It highlights that even minor misalignments in bulk data processing at high levels can trigger massive technical debt, necessitating senior-level intervention to ensure 100% billing accuracy and prevent legal-compliance failures.</t>
+    </r>
+  </si>
+  <si>
+    <t>Forensic Audit &amp; API Restoration</t>
+  </si>
+  <si>
+    <t>CRM Disaster Recovery &amp; Data Integrity</t>
+  </si>
+  <si>
+    <r>
+      <t>Emergency Structural Reconstruction:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Recreated the comprehensive Karbon profile for </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>COTO SOLORZANO, HUGO ERNESTO &amp; ALVARADO ORELLANA, DIANA - 4670</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> following an accidental deletion. Utilized legacy </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unique Client ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mapping and historical process logs to restore profile metadata. Re-established the technical link between the individual and the associated corporate entity. Manually reconstructed the specific Tax Work item and audited the workstream to identify missing documentation, providing a precise recovery roadmap for the staff to finalize the file.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Business Continuity &amp; Crisis Management:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mitigated the impact of human error on the firm’s core CRM. By leveraging the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unique Client ID architecture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, I ensured that the restored data remained consistent with the global database. This operation required high-tier attention to detail to ensure no historical tax data was lost, emphasizing that a single accidental deletion necessitates a multi-day technical recovery to guarantee service continuity.</t>
+    </r>
+  </si>
+  <si>
+    <t>Disaster Recovery / Integrity</t>
+  </si>
+  <si>
+    <t>Strategic Federal Credentialing &amp; AI Compliance</t>
+  </si>
+  <si>
+    <t>Advanced Data Analytics &amp; Reporting</t>
+  </si>
+  <si>
+    <t>[Link]</t>
+  </si>
+  <si>
+    <t>Mar 13 - 19</t>
+  </si>
+  <si>
+    <r>
+      <t>Data Governance &amp; RPA Workaround:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Overcame API architectural limitations in Karbon and Square by implementing a secondary data validation layer within ProSeries. This ensured the accuracy of growth metrics and marketing ROI.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sr.Data Integrity</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Investigated and resolved the inability to track new clients through Karbon API (due to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>LastModified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> date limitations) and Square (due to profile duplication and multi-family appointments). Developed a workaround by reverse-engineering </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ProSeries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reports, isolating the "Transfer Log" and identifying clients created from scratch versus those transferred from previous years. Finalized a report identifying </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>418 new clients</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for 1040 and 1120 forms.</t>
+    </r>
+  </si>
+  <si>
+    <t>System Integration &amp; API Optimization</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Diagnosed and patched a critical data mapping failure in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MEGA - SquareUp API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> integration. Identified that client records were appearing as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Unknown"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> due to non-standard data entry in Square (Quick Creation/Single Field Name entries). Reconfigured the bot's parsing logic within MEGA to handle three distinct naming conventions: "Given Name" (Quick Entry), Split Name (First/Middle/Last), and "Company Name" for entity-based records.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Interoperability &amp; Data Integrity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resolved an API parsing conflict to ensure seamless data flow between payment processing and the management platform. By implementing multi-method validation logic, I prevented malformed data from corrupting the database and eliminated "Unknown" identifiers.</t>
+    </r>
+  </si>
+  <si>
+    <t>Automation / Infrastructure</t>
+  </si>
+  <si>
+    <t>Mar 19 - 23</t>
+  </si>
+  <si>
+    <t>Data Governance &amp; AI Security Policy</t>
+  </si>
+  <si>
+    <r>
+      <t>Risk Mitigation &amp; Data Sovereignty:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Established a strategic framework to prevent unauthorized data training and potential leaks. By distinguishing between "Free Tier" vulnerabilities and Enterprise-level encryption, I secured the firm’s intellectual property and client confidentiality under international data protection standards.</t>
+    </r>
+  </si>
+  <si>
+    <t>Legal Compliance / Sr. Consulting</t>
+  </si>
+  <si>
+    <t>Mar 25</t>
+  </si>
+  <si>
+    <t>Defined and deployed a corporate AI Security Policy following a consultation with Christian regarding the leakage of privileged client information (SSN, Bank Accounts). Conducted a technical audit of the privacy clauses in Google Workspace for Education/Business (Gemini) versus Public LLMs (ChatGPT, Perplexity, Claude). Formulated and distributed a firm-wide directive establishing Gemini and TaxGPT as the only authorized tools, specifically enforcing the use of the @jw-accounting.com domain to leverage Enterprise-grade data protection.</t>
+  </si>
+  <si>
     <r>
       <t>Interoperability &amp; Advanced RBAC:</t>
     </r>
@@ -1440,583 +2196,81 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Solving a critical data security gap by filtering sensitive firm-wide revenue data. The system enables General Management (Nathaly) to pivot between global metrics and individual performance views, providing high-fidelity oversight while ensuring staff only access authorized, acoted data.</t>
-    </r>
-  </si>
-  <si>
-    <t>Software R&amp;D / Data Governance</t>
-  </si>
-  <si>
-    <t>IT Infrastructure &amp; Disaster Recovery</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Comprehensive manual backup of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ProSeries 25Data</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> files. Execution of data redundancy protocols by migrating tax year datasets to independent, secure external storage sources.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Business Continuity &amp; Risk Mitigation:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Implementing a fail-safe data architecture to prevent information loss during Tax Season. This redundancy layer protects critical client tax records against system failures or software corruption, ensuring 100% data integrity and operational resilience.</t>
-    </r>
-  </si>
-  <si>
-    <t>Infrastructure / Risk Management</t>
-  </si>
-  <si>
-    <t>Financial Systems &amp; API Infrastructure</t>
-  </si>
-  <si>
-    <t>Mar 11-12</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Responded to Co-Owner Christian Velasquez regarding Square daily sales report timing. Conducted a technical audit of Square’s settlement windows and bank clearing cycles. Identified that shifting the closing time from 8:00 PM to 11:00 PM triggers a 48-hour delay in fund availability. Evaluated Square's "Instant Transfer" 1.95% fee and rejected it. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Implemented a hybrid configuration: optimized the cutoff to 12:00 AM (midnight) to capture a full 24-hour cycle (including late-night invoices) without additional settlement delays. Scheduled a rollback to the original 8:00 PM configuration for April 17 to restore 24-hour liquidity (T+1) post-peak season.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Data Governance &amp; Cash Flow Optimization:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Orchestrated a strategic workaround to balance operational visibility against liquidity needs. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Engineered a hybrid scheduling model: prioritizing 24H data integrity during Tax Season and transitioning back to accelerated cash flow (Next-Day Refund) post-April 17.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Mitigated unnecessary overhead while ensuring system resilience.</t>
-    </r>
-  </si>
-  <si>
-    <t>Financial Infrastructure / RPA Workaround</t>
-  </si>
-  <si>
-    <t>Mar 07</t>
-  </si>
-  <si>
-    <t>Mar 9</t>
-  </si>
-  <si>
-    <t>Mar 10</t>
-  </si>
-  <si>
-    <t>Evolution &amp; Growth</t>
-  </si>
-  <si>
-    <t>Strategic High-Level Consulting</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Engineered the Final Version of the Deleon Creative LLC Contract incorporating an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AI-Shielded Response Strategy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Detected that external contract modifications were being autonomously generated by third-party AI; developed a counter-strategy to neutralize non-expert algorithmic suggestions. Provided CEO Diego with the final instrument and the precise technical framework for contractual drafting.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Adversarial AI Mitigation:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Protecting firm interests by identifying and neutralizing hallucinated or suboptimal AI-generated legal clauses. Established a "Shielded Response" protocol to maintain human-expert governance over automated interference.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Performed final forensic audit of the DeLeon contract. Identified critical date inconsistencies and validated salary evolution parameters. Addressed a high-risk structural conflict regarding </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Florida Labor Law (Dual Employee/Employer status for Ana)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Strategically withheld a new redacted document to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prevent recursive AI friction</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, delivering instead a final expert resolution. Case closed to full client satisfaction.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Legal-Technical Compliance:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resolved complex employment status paradoxes under Florida jurisdiction. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Advanced Consulting:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Utilized a "Communication-Only" strategy to bypass the client's AI feedback loop, ensuring structural integrity without triggering further automated errors.</t>
-    </r>
-  </si>
-  <si>
-    <t>Feb 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb 3 </t>
-  </si>
-  <si>
-    <t>Omnichannel AI Integration &amp; Lead Governance</t>
-  </si>
-  <si>
-    <t>Feb 14 - Ongoing</t>
-  </si>
-  <si>
-    <r>
-      <t>Interoperability &amp; AI Governance:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Establishing the foundational "Zero-Latency" lead capture system. By utilizing a proprietary System Prompt and API-level integration, we are securing a scalable, 24/7 automated response ecosystem that bypasses manual oversight while maintaining brand voice and data integrity.</t>
-    </r>
-  </si>
-  <si>
-    <t>AI Ecosystem Deployment</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Mar 9 - Ongoing</t>
-  </si>
-  <si>
-    <r>
-      <t>Official WhatsApp Business &amp; Gemini AI Infrastructure Deployment:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Successfully provisioned the official J&amp;W WhatsApp Business line. Engineered a direct API bridge using a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Google AI Studio Token</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and the WhatAuto middleware to link conversational flows with a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Gemini Flash model</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Developed and deployed the initial </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>System Prompt Architecture</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to define the AI's persona, constraints, and business logic for preliminary engagement testing.</t>
-    </r>
-  </si>
-  <si>
-    <t>Financial Data Governance &amp; Forensic Audit</t>
-  </si>
-  <si>
-    <t>Mar 13 - 14</t>
-  </si>
-  <si>
-    <r>
-      <t>Massive Systemic Data Recovery &amp; Audit:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Initiated an emergency technical intervention following a report from Management containing critical email discrepancies. Identified that the source of the error was an external report with misaligned data that compromised profile integrity. To resolve this, I engineered a high-scale extraction of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5,932 total client records</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> via Square API. Conducted a targeted forensic audit of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3,889 individual accounts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to isolate a legacy "column-shift" error. After an exhaustive profile-by-profile verification to protect recent manual updates, I executed a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bulk API restoration of 157 corrupted records</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, re-establishing the "Source of Truth" for the firm.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Advanced System Resilience:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Mitigated the high-risk fallout of data corruption originated at the managerial report level. This operation required extensive technical man-hours to reconstruct data lineage without original CSV logs. It highlights that even minor misalignments in bulk data processing at high levels can trigger massive technical debt, necessitating senior-level intervention to ensure 100% billing accuracy and prevent legal-compliance failures.</t>
-    </r>
-  </si>
-  <si>
-    <t>Forensic Audit &amp; API Restoration</t>
-  </si>
-  <si>
-    <t>CRM Disaster Recovery &amp; Data Integrity</t>
-  </si>
-  <si>
-    <r>
-      <t>Emergency Structural Reconstruction:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Recreated the comprehensive Karbon profile for </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>COTO SOLORZANO, HUGO ERNESTO &amp; ALVARADO ORELLANA, DIANA - 4670</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> following an accidental deletion. Utilized legacy </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Unique Client ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> mapping and historical process logs to restore profile metadata. Re-established the technical link between the individual and the associated corporate entity. Manually reconstructed the specific Tax Work item and audited the workstream to identify missing documentation, providing a precise recovery roadmap for the staff to finalize the file.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Business Continuity &amp; Crisis Management:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Mitigated the impact of human error on the firm’s core CRM. By leveraging the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Unique Client ID architecture</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, I ensured that the restored data remained consistent with the global database. This operation required high-tier attention to detail to ensure no historical tax data was lost, emphasizing that a single accidental deletion necessitates a multi-day technical recovery to guarantee service continuity.</t>
-    </r>
-  </si>
-  <si>
-    <t>Disaster Recovery / Integrity</t>
-  </si>
-  <si>
-    <t>Strategic Federal Credentialing &amp; AI Compliance</t>
+      <t xml:space="preserve"> Solving a critical data security gap by filtering sensitive firm-wide revenue data. The system enables General Management (Nathalie) to pivot between global metrics and individual performance views, providing high-fidelity oversight while ensuring staff only access authorized, acoted data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Apr 6</t>
+  </si>
+  <si>
+    <r>
+      <t>Proposal for Advanced Data Restructuring:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Technical roadmap to transition from simple revenue tracking to granular volume/quantity analytics. Includes the development of new visualizations and a mandatory architectural shift: associating every payment with a specific Invoice Code to resolve record inflation caused by partial payments. The proposal includes a feasibility study for a legacy-data matching protocol to align historical payments with old invoices and expanding data schemas to capture specific line items beyond general department categories.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>System Resilience &amp; Scalability:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Engineering a solution for the "Partial Payment Multiplicity" issue. By restructuring the data schema to be Invoice-centric rather than Transaction-centric, we eliminate data noise and enable precise KPI tracking. This is a prerequisite for moving from basic BI to automated financial forecasting and granular performance auditing.</t>
+    </r>
+  </si>
+  <si>
+    <t>Data Architecture / R&amp;D</t>
+  </si>
+  <si>
+    <t>Technical Support &amp; System Troubleshooting</t>
+  </si>
+  <si>
+    <r>
+      <t>System Resilience &amp; Cache Governance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resolved a critical data-visibility gap that prevented the tax preparer from accessing 2024 payment records. By bypassing standard transfer protocols and performing manual cache-level reconciliation, I prevented potential data loss and ensured the firm’s electronic filing (EF) continuity during a time-sensitive period.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sr. Consulting / Crisis Leadership</t>
+  </si>
+  <si>
+    <t>Stakeholder Support (Daniela Moncada): Critical recovery of the Tax Return for "Escobar, Juan Pablo &amp; Vitanzo Janet" in ProSeries 2024. Performed a forensic audit of local cache files to resolve a naming conflict and synchronization failure. Identified the most recent data state by comparing modification timestamps between redundant cache files (Old Name vs. New Name). Executed a manual file-name rollback to re-establish database handshaking with ProSeries 24, enabling the file to correctly status as "Marked for EF" in the EF Center for processing.</t>
+  </si>
+  <si>
+    <t>Mar 9 - Apr 3</t>
+  </si>
+  <si>
+    <t>Apr 3 - Future</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2052,6 +2306,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2300,14 +2560,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:S108"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="32.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="84.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2345,7 +2605,7 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -2381,7 +2641,7 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2417,7 +2677,7 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -2453,7 +2713,7 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2489,7 +2749,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -2525,7 +2785,7 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2561,7 +2821,7 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2597,7 +2857,7 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -2633,7 +2893,7 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -2669,7 +2929,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -2705,7 +2965,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -2741,7 +3001,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -2777,7 +3037,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -2813,7 +3073,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2849,7 +3109,7 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2885,7 +3145,7 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -2921,7 +3181,7 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -2957,7 +3217,7 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -2993,7 +3253,7 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -3029,7 +3289,7 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:19" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -3065,7 +3325,7 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:19" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -3101,7 +3361,7 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -3137,7 +3397,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -3173,7 +3433,7 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -3209,7 +3469,7 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
@@ -3245,7 +3505,7 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>7</v>
       </c>
@@ -3281,7 +3541,7 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -3317,7 +3577,7 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
@@ -3353,7 +3613,7 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
@@ -3389,7 +3649,7 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:19" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -3425,7 +3685,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:19" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -3461,7 +3721,7 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:19" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -3497,7 +3757,7 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:19" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
@@ -3533,7 +3793,7 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:19" ht="15.75" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
@@ -3569,7 +3829,7 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
     </row>
-    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:19" ht="15.75" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
@@ -3605,7 +3865,7 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:19" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>11</v>
       </c>
@@ -3641,7 +3901,7 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:19" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
@@ -3677,7 +3937,7 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
     </row>
-    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:19" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -3713,7 +3973,7 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
     </row>
-    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:19" ht="15.75" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -3749,7 +4009,7 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
     </row>
-    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:19" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -3785,7 +4045,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
     </row>
-    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:19" ht="15.75" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -3821,7 +4081,7 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
     </row>
-    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:19" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -3857,7 +4117,7 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:19" ht="15.75" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -3893,7 +4153,7 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
     </row>
-    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:19" ht="15.75" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>11</v>
       </c>
@@ -3929,7 +4189,7 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
     </row>
-    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:19" ht="15.75" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
@@ -3965,7 +4225,7 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:19" ht="15.75" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>11</v>
       </c>
@@ -4001,7 +4261,7 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
     </row>
-    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:19" ht="15.75" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -4037,7 +4297,7 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:19" ht="15.75" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>11</v>
       </c>
@@ -4073,7 +4333,7 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
     </row>
-    <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:19" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -4109,7 +4369,7 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
     </row>
-    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:19" ht="15.75" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
@@ -4145,7 +4405,7 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
     </row>
-    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:19" ht="15.75" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>11</v>
       </c>
@@ -4181,7 +4441,7 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
     </row>
-    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:19" ht="15.75" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>11</v>
       </c>
@@ -4217,7 +4477,7 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
     </row>
-    <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:19" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>11</v>
       </c>
@@ -4253,7 +4513,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
     </row>
-    <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:19" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>11</v>
       </c>
@@ -4289,7 +4549,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:19" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -4325,7 +4585,7 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
     </row>
-    <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:19" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
@@ -4361,7 +4621,7 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
     </row>
-    <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:19" ht="15.75" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
@@ -4397,7 +4657,7 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
     </row>
-    <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:19" ht="15.75" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -4433,7 +4693,7 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
     </row>
-    <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:19" ht="15.75" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>11</v>
       </c>
@@ -4469,7 +4729,7 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
     </row>
-    <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:19" ht="15.75" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>11</v>
       </c>
@@ -4505,7 +4765,7 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
     </row>
-    <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:19" ht="15.75" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
@@ -4541,7 +4801,7 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
     </row>
-    <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:19" ht="15.75" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
@@ -4577,7 +4837,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:19" ht="15.75" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -4613,7 +4873,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:19" ht="15.75" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
@@ -4649,7 +4909,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:19" ht="15.75" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -4685,22 +4945,22 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:19" ht="15.75" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E67" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>193</v>
@@ -4721,22 +4981,22 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:19" ht="13">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>73</v>
@@ -4757,7 +5017,7 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:19" ht="15.75" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
@@ -4793,7 +5053,7 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:19" ht="13">
       <c r="A70" s="2" t="s">
         <v>11</v>
       </c>
@@ -4829,7 +5089,7 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:19" ht="13">
       <c r="A71" s="2" t="s">
         <v>11</v>
       </c>
@@ -4865,7 +5125,7 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:19" ht="13">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -4901,7 +5161,7 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:19" ht="13">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
@@ -4937,7 +5197,7 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:19" ht="13">
       <c r="A74" s="2" t="s">
         <v>11</v>
       </c>
@@ -4973,7 +5233,7 @@
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:19" ht="13">
       <c r="A75" s="2" t="s">
         <v>11</v>
       </c>
@@ -5009,7 +5269,7 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:19" ht="13">
       <c r="A76" s="2" t="s">
         <v>11</v>
       </c>
@@ -5043,7 +5303,7 @@
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
     </row>
-    <row r="77" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:19" ht="13">
       <c r="A77" s="2" t="s">
         <v>11</v>
       </c>
@@ -5070,7 +5330,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:19" ht="13">
       <c r="A78" s="2" t="s">
         <v>11</v>
       </c>
@@ -5097,7 +5357,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:19" ht="13">
       <c r="A79" s="2" t="s">
         <v>11</v>
       </c>
@@ -5124,7 +5384,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:19" ht="13">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -5151,7 +5411,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" ht="13">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -5178,7 +5438,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" ht="13">
       <c r="A82" s="2" t="s">
         <v>11</v>
       </c>
@@ -5205,7 +5465,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" ht="13">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -5232,7 +5492,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" ht="13">
       <c r="A84" s="2" t="s">
         <v>11</v>
       </c>
@@ -5259,7 +5519,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" ht="13">
       <c r="A85" s="2" t="s">
         <v>11</v>
       </c>
@@ -5286,7 +5546,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" ht="13">
       <c r="A86" s="2" t="s">
         <v>11</v>
       </c>
@@ -5313,7 +5573,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="13" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" ht="13">
       <c r="A87" s="2" t="s">
         <v>11</v>
       </c>
@@ -5340,26 +5600,26 @@
         <v>53</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" ht="15.75" customHeight="1">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>445</v>
-      </c>
       <c r="H88" s="2" t="s">
         <v>9</v>
       </c>
@@ -5367,7 +5627,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9" ht="15.75" customHeight="1">
       <c r="A89" s="2" t="s">
         <v>11</v>
       </c>
@@ -5394,7 +5654,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" ht="15.75" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>11</v>
       </c>
@@ -5421,7 +5681,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>11</v>
       </c>
@@ -5448,7 +5708,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>11</v>
       </c>
@@ -5474,12 +5734,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>389</v>
@@ -5500,16 +5760,16 @@
         <v>54</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>393</v>
@@ -5527,15 +5787,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>396</v>
@@ -5553,34 +5813,34 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" ht="15.75" customHeight="1">
       <c r="A96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="G96" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="H96" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="97" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:9" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>12</v>
       </c>
@@ -5588,25 +5848,25 @@
         <v>406</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>407</v>
       </c>
       <c r="F97" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="G97" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="H97" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>12</v>
       </c>
@@ -5633,12 +5893,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9" ht="15.75" customHeight="1">
       <c r="A99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="5" t="s">
@@ -5660,12 +5920,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9" ht="15.75" customHeight="1">
       <c r="A100" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="5" t="s">
@@ -5687,53 +5947,53 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:9" ht="15.75" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E101" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="G101" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="H101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="F102" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>418</v>
-      </c>
       <c r="H102" s="2" t="s">
         <v>9</v>
       </c>
@@ -5741,31 +6001,168 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:9" ht="15.75" customHeight="1">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="G103" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/SMEAC_Master_Data.xlsx
+++ b/SMEAC_Master_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vargas/Documents/JW/Proyectos 2025-2026/IT-Projects-J-W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C874D27A-53FB-7F45-97A2-800467C965C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4094BF30-90DE-464F-B21A-7D6FF8D78694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="680" windowWidth="25460" windowHeight="18780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5860,7 +5860,7 @@
         <v>408</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>54</v>
